--- a/Documents/agregar ejemplo.xlsx
+++ b/Documents/agregar ejemplo.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +27,7 @@
   <fonts count="4">
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -105,20 +105,126 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>